--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_0_15.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/1500000/Output_0_15.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>716371.8036446582</v>
+        <v>716379.1415249447</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>925658.2446351657</v>
+        <v>925399.3994514382</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18327269.62422524</v>
+        <v>18327015.93006067</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5283567.215382138</v>
+        <v>5283674.776931893</v>
       </c>
     </row>
     <row r="11">
@@ -694,28 +694,28 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>21.15688084962317</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>241</v>
+        <v>212.285385643442</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="3">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50.0165318697929</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -785,16 +785,16 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -825,10 +825,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>39.82778746869526</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -849,10 +849,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>47.02492433367362</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -904,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -928,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -946,13 +946,13 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>220.8569218604367</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>241</v>
+        <v>212.285385643442</v>
       </c>
     </row>
     <row r="6">
@@ -962,16 +962,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -980,13 +980,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>85.31372784089211</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1010,28 +1010,28 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.778505492039412</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="7">
@@ -1086,10 +1086,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.809496073036188</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1250,25 +1250,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
-        <v>15.37950989044974</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>241</v>
+        <v>3.833957768458675</v>
       </c>
       <c r="X9" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1293,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1323,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1366,19 +1366,19 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G11" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H11" t="n">
-        <v>202.2821007854552</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>52.42556848774763</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1436,25 +1436,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>33.63631471189681</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1484,22 +1484,22 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>4.580549094716531</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1536,10 +1536,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>14.83685490770591</v>
       </c>
       <c r="J13" t="n">
-        <v>24.75543250779077</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
         <v>22.26949182588285</v>
@@ -1557,10 +1557,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1606,19 +1606,19 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>40.476279133135</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1639,10 +1639,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>146.1378473354543</v>
+        <v>145.4467082856154</v>
       </c>
       <c r="D15" t="n">
         <v>147.4450655646388</v>
@@ -1697,7 +1697,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>17.55829564281238</v>
+        <v>14.83685490770591</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1849,13 +1849,13 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.79691042959408</v>
+        <v>241.014288877659</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>190.3453970742847</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -1973,7 +1973,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
-        <v>4.525096818297269</v>
+        <v>4.58054909471631</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -2043,22 +2043,22 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2077,19 +2077,19 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="F20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2119,25 +2119,25 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>223.0958495641314</v>
+        <v>1.809496073036357</v>
       </c>
       <c r="U20" t="n">
-        <v>21.15688084962317</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
     </row>
     <row r="21">
@@ -2147,28 +2147,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>150.3737494689905</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>71.21159262491652</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2210,13 +2210,13 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="C23" t="n">
-        <v>212.2728000000115</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -2359,22 +2359,22 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
     </row>
     <row r="24">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>95.77809019286784</v>
       </c>
       <c r="C24" t="n">
-        <v>116.651914997863</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2441,16 +2441,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>190.3453970742848</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2554,16 +2554,16 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>200.3235106453875</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2599,19 +2599,19 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="27">
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>56.17030901074568</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2675,22 +2675,22 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>69.84652554504288</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -2779,31 +2779,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>5.877922149011282e-11</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2824,7 +2824,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2839,13 +2839,13 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>212.2728000000434</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>241</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>50.05769526855291</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>29.75784556612239</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3019,7 +3019,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -3028,10 +3028,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>5.877922149011282e-11</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3064,28 +3064,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>112.2877629085169</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>212.2853856434422</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
     </row>
     <row r="33">
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>50.0165318697929</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3152,19 +3152,19 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>29.79900896488246</v>
       </c>
     </row>
     <row r="34">
@@ -3234,10 +3234,10 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>202.2821007854552</v>
+        <v>241.014288877659</v>
       </c>
       <c r="D35" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3316,13 +3316,13 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>212.2853856434422</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3389,19 +3389,19 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>50.01653186979276</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X36" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>205.6826957773044</v>
+        <v>29.79900896488246</v>
       </c>
     </row>
     <row r="37">
@@ -3465,13 +3465,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -3490,25 +3490,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>212.2728000000159</v>
+        <v>241.014288877659</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
     </row>
     <row r="39">
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>45.28887413297223</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3617,28 +3617,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>70.59311687130074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="C41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3739,13 +3739,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3784,19 +3784,19 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
     </row>
     <row r="42">
@@ -3809,28 +3809,28 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3860,22 +3860,22 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>56.72249065605558</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>109.4031921034046</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="43">
@@ -3900,13 +3900,13 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3970,25 +3970,25 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>208.2638363878123</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>70.3171332801741</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R44" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -4021,13 +4021,13 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -4055,10 +4055,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>122.5487952068456</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>112.2354442364965</v>
@@ -4097,16 +4097,16 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9413820809748</v>
+        <v>3.297399598374966</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W45" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -4143,43 +4143,43 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4289,76 +4289,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K2" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L2" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M2" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N2" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O2" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R2" t="n">
-        <v>942.6294132832089</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S2" t="n">
-        <v>731.498029862759</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T2" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U2" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V2" t="n">
-        <v>19.28</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W2" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X2" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="3">
@@ -4368,76 +4368,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C3" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D3" t="n">
-        <v>19.28</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E3" t="n">
-        <v>19.28</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F3" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G3" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H3" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I3" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K3" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L3" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M3" t="n">
-        <v>613.1906659261865</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N3" t="n">
-        <v>656.0154414866706</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O3" t="n">
-        <v>894.6054414866707</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P3" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V3" t="n">
-        <v>728.8478917682573</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W3" t="n">
-        <v>485.4135483339139</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X3" t="n">
-        <v>277.5620481283811</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y3" t="n">
-        <v>69.80174936342718</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="4">
@@ -4447,76 +4447,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I4" t="n">
-        <v>19.28</v>
+        <v>113.583345248266</v>
       </c>
       <c r="J4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L4" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M4" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N4" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q4" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="5">
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>243.9518979040591</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C5" t="n">
-        <v>243.9518979040591</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D5" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E5" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F5" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G5" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H5" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I5" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K5" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L5" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M5" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N5" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O5" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V5" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W5" t="n">
-        <v>730.820584772746</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X5" t="n">
-        <v>487.3862413384025</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y5" t="n">
-        <v>243.9518979040591</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.03413265278571</v>
+        <v>588.0815197256143</v>
       </c>
       <c r="C6" t="n">
-        <v>20.03413265278571</v>
+        <v>413.6284904444873</v>
       </c>
       <c r="D6" t="n">
-        <v>20.03413265278571</v>
+        <v>264.694080783236</v>
       </c>
       <c r="E6" t="n">
-        <v>20.03413265278571</v>
+        <v>105.4566257777805</v>
       </c>
       <c r="F6" t="n">
-        <v>20.03413265278571</v>
+        <v>105.4566257777805</v>
       </c>
       <c r="G6" t="n">
-        <v>20.03413265278571</v>
+        <v>105.4566257777805</v>
       </c>
       <c r="H6" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I6" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K6" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L6" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M6" t="n">
-        <v>542.7665223866492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N6" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O6" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R6" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S6" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T6" t="n">
-        <v>487.2265313623206</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U6" t="n">
-        <v>259.0029130987097</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V6" t="n">
-        <v>23.85080486696694</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W6" t="n">
-        <v>20.03413265278571</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X6" t="n">
-        <v>20.03413265278571</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y6" t="n">
-        <v>20.03413265278571</v>
+        <v>756.2968567456824</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L7" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M7" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N7" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q7" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V7" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>506.1486868686869</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C8" t="n">
-        <v>262.7143434343434</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="D8" t="n">
-        <v>262.7143434343434</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="E8" t="n">
-        <v>262.7143434343434</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="F8" t="n">
-        <v>262.7143434343434</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="G8" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="H8" t="n">
-        <v>19.28</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="I8" t="n">
-        <v>19.28</v>
+        <v>21.10891692136039</v>
       </c>
       <c r="J8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K8" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L8" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M8" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N8" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O8" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X8" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y8" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I9" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K9" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L9" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M9" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N9" t="n">
-        <v>781.3565223866492</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O9" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P9" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R9" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S9" t="n">
-        <v>862.8304705528857</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T9" t="n">
-        <v>862.8304705528857</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U9" t="n">
-        <v>862.8304705528857</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V9" t="n">
-        <v>847.2956120776839</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="W9" t="n">
-        <v>603.8612686433405</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="X9" t="n">
-        <v>396.0097684378077</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="Y9" t="n">
-        <v>188.2494696728538</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L10" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M10" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q10" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="C11" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="D11" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="E11" t="n">
-        <v>710.4740411974295</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="F11" t="n">
-        <v>467.0396977630861</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="G11" t="n">
-        <v>223.6053543287427</v>
+        <v>315.6850394389064</v>
       </c>
       <c r="H11" t="n">
-        <v>19.28</v>
+        <v>72.23626279480629</v>
       </c>
       <c r="I11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K11" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L11" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M11" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N11" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O11" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q11" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R11" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S11" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T11" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="U11" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="V11" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="W11" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="X11" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="Y11" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>795.7846629799319</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C12" t="n">
-        <v>621.3316336988049</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D12" t="n">
-        <v>472.3972240375537</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E12" t="n">
-        <v>313.1597690320982</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F12" t="n">
-        <v>166.6252110589831</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G12" t="n">
-        <v>132.6491355924207</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L12" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M12" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="N12" t="n">
-        <v>473.3719638733197</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="O12" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P12" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R12" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S12" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T12" t="n">
-        <v>964</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U12" t="n">
-        <v>964</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V12" t="n">
-        <v>964</v>
+        <v>23.90796037760316</v>
       </c>
       <c r="W12" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X12" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y12" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="C13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="D13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="E13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="F13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="G13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="H13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="I13" t="n">
-        <v>66.7799235693673</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J13" t="n">
-        <v>41.77443618776046</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L13" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M13" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N13" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P13" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="R13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="S13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="T13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="U13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="V13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="W13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="X13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Y13" t="n">
-        <v>66.7799235693673</v>
+        <v>151.0645035650224</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19.28</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="C14" t="n">
-        <v>19.28</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="D14" t="n">
-        <v>19.28</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="E14" t="n">
-        <v>19.28</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="F14" t="n">
-        <v>19.28</v>
+        <v>559.1338160830062</v>
       </c>
       <c r="G14" t="n">
-        <v>19.28</v>
+        <v>315.6850394389062</v>
       </c>
       <c r="H14" t="n">
-        <v>19.28</v>
+        <v>72.23626279480618</v>
       </c>
       <c r="I14" t="n">
-        <v>19.28</v>
+        <v>31.35113235729607</v>
       </c>
       <c r="J14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K14" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L14" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M14" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N14" t="n">
-        <v>725.144994565301</v>
+        <v>725.202150075937</v>
       </c>
       <c r="O14" t="n">
-        <v>874.339944707949</v>
+        <v>874.397100218585</v>
       </c>
       <c r="P14" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q14" t="n">
-        <v>964</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="R14" t="n">
-        <v>964</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="S14" t="n">
-        <v>964</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="T14" t="n">
-        <v>964</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="U14" t="n">
-        <v>964</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="V14" t="n">
-        <v>964</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="W14" t="n">
-        <v>720.5656565656566</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="X14" t="n">
-        <v>506.1486868686869</v>
+        <v>802.5825927271062</v>
       </c>
       <c r="Y14" t="n">
-        <v>262.7143434343434</v>
+        <v>802.5825927271062</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="C15" t="n">
-        <v>816.3860127924704</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D15" t="n">
-        <v>667.4516031312191</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E15" t="n">
-        <v>508.2141481257637</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F15" t="n">
-        <v>361.6795901526487</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G15" t="n">
-        <v>222.9487647352642</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H15" t="n">
-        <v>109.5796291428435</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I15" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K15" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L15" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M15" t="n">
-        <v>542.7665223866492</v>
+        <v>304.2053859195203</v>
       </c>
       <c r="N15" t="n">
-        <v>542.7665223866492</v>
+        <v>542.8095319084027</v>
       </c>
       <c r="O15" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972852</v>
       </c>
       <c r="P15" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q15" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R15" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S15" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T15" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U15" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V15" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="W15" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="X15" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Y15" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="C16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="D16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="E16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="F16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="G16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="H16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="I16" t="n">
-        <v>136.0766383258138</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J16" t="n">
-        <v>41.77443618776046</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L16" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M16" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N16" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Q16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="R16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="S16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="T16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="U16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="V16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="W16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="X16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
       <c r="Y16" t="n">
-        <v>153.8122904902707</v>
+        <v>151.0645035650224</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>233.6969696969697</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="C17" t="n">
-        <v>233.6969696969697</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="D17" t="n">
-        <v>233.6969696969697</v>
+        <v>710.5167634983089</v>
       </c>
       <c r="E17" t="n">
-        <v>233.6969696969697</v>
+        <v>467.0679868542089</v>
       </c>
       <c r="F17" t="n">
-        <v>233.6969696969697</v>
+        <v>467.0679868542089</v>
       </c>
       <c r="G17" t="n">
-        <v>233.6969696969697</v>
+        <v>467.0679868542089</v>
       </c>
       <c r="H17" t="n">
-        <v>231.8819086569757</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="I17" t="n">
-        <v>19.28</v>
+        <v>31.35113235729607</v>
       </c>
       <c r="J17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K17" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L17" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M17" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N17" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759371</v>
       </c>
       <c r="O17" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185851</v>
       </c>
       <c r="P17" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q17" t="n">
-        <v>964</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="R17" t="n">
-        <v>964</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="S17" t="n">
-        <v>964</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="T17" t="n">
-        <v>964</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="U17" t="n">
-        <v>964</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="V17" t="n">
-        <v>720.5656565656566</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="W17" t="n">
-        <v>477.1313131313132</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="X17" t="n">
-        <v>233.6969696969697</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="Y17" t="n">
-        <v>233.6969696969697</v>
+        <v>953.9655401424089</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K18" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L18" t="n">
-        <v>19.28</v>
+        <v>374.6018090363992</v>
       </c>
       <c r="M18" t="n">
-        <v>257.87</v>
+        <v>374.6018090363992</v>
       </c>
       <c r="N18" t="n">
-        <v>496.46</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="O18" t="n">
-        <v>735.0500000000001</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P18" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q18" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R18" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="S18" t="n">
-        <v>689.4131260035546</v>
+        <v>689.4702815141906</v>
       </c>
       <c r="T18" t="n">
-        <v>487.2265313623206</v>
+        <v>487.2836868729566</v>
       </c>
       <c r="U18" t="n">
-        <v>259.0029130987097</v>
+        <v>259.0600686093456</v>
       </c>
       <c r="V18" t="n">
-        <v>23.85080486696694</v>
+        <v>23.90796037760293</v>
       </c>
       <c r="W18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L19" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M19" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N19" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>262.7143434343434</v>
+        <v>718.7806050553884</v>
       </c>
       <c r="C20" t="n">
-        <v>262.7143434343434</v>
+        <v>718.7806050553884</v>
       </c>
       <c r="D20" t="n">
-        <v>262.7143434343434</v>
+        <v>718.7806050553884</v>
       </c>
       <c r="E20" t="n">
-        <v>262.7143434343434</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="F20" t="n">
-        <v>19.28</v>
+        <v>475.3318284112884</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>752.8686165795501</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>527.519273585478</v>
+        <v>962.2293816994884</v>
       </c>
       <c r="U20" t="n">
-        <v>506.1486868686869</v>
+        <v>962.2293816994884</v>
       </c>
       <c r="V20" t="n">
-        <v>506.1486868686869</v>
+        <v>962.2293816994884</v>
       </c>
       <c r="W20" t="n">
-        <v>262.7143434343434</v>
+        <v>962.2293816994884</v>
       </c>
       <c r="X20" t="n">
-        <v>262.7143434343434</v>
+        <v>962.2293816994884</v>
       </c>
       <c r="Y20" t="n">
-        <v>262.7143434343434</v>
+        <v>718.7806050553884</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>171.1726762313035</v>
+        <v>487.2836868729566</v>
       </c>
       <c r="C21" t="n">
-        <v>19.28</v>
+        <v>487.2836868729566</v>
       </c>
       <c r="D21" t="n">
-        <v>19.28</v>
+        <v>487.2836868729566</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>328.0462318675011</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>181.5116738943861</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>181.5116738943861</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363992</v>
       </c>
       <c r="M21" t="n">
-        <v>304.1765223866491</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="N21" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="S21" t="n">
-        <v>790.5826554506689</v>
+        <v>689.4702815141906</v>
       </c>
       <c r="T21" t="n">
-        <v>790.5826554506689</v>
+        <v>487.2836868729566</v>
       </c>
       <c r="U21" t="n">
-        <v>790.5826554506689</v>
+        <v>487.2836868729566</v>
       </c>
       <c r="V21" t="n">
-        <v>790.5826554506689</v>
+        <v>487.2836868729566</v>
       </c>
       <c r="W21" t="n">
-        <v>547.1483120163255</v>
+        <v>487.2836868729566</v>
       </c>
       <c r="X21" t="n">
-        <v>547.1483120163255</v>
+        <v>487.2836868729566</v>
       </c>
       <c r="Y21" t="n">
-        <v>339.3880132513715</v>
+        <v>487.2836868729566</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>233.6969696969813</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935105105</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951691</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580732</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.1449945653126</v>
+        <v>725.2021500759371</v>
       </c>
       <c r="O23" t="n">
-        <v>874.3399447079606</v>
+        <v>874.3971002185851</v>
       </c>
       <c r="P23" t="n">
-        <v>964.0000000000116</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q23" t="n">
-        <v>964.0000000000116</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R23" t="n">
-        <v>964.0000000000116</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S23" t="n">
-        <v>964.0000000000116</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T23" t="n">
-        <v>964.0000000000116</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="U23" t="n">
-        <v>964.0000000000116</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="V23" t="n">
-        <v>964.0000000000116</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="W23" t="n">
-        <v>720.5656565656682</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="X23" t="n">
-        <v>477.1313131313248</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="Y23" t="n">
-        <v>233.6969696969813</v>
+        <v>262.7299197543127</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>137.1102171695586</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="C24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="D24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363992</v>
       </c>
       <c r="M24" t="n">
-        <v>487.8331058683492</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="N24" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="O24" t="n">
-        <v>781.3565223866492</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S24" t="n">
-        <v>790.5826554506689</v>
+        <v>790.6398109613049</v>
       </c>
       <c r="T24" t="n">
-        <v>588.3960608094349</v>
+        <v>588.4532163200709</v>
       </c>
       <c r="U24" t="n">
-        <v>588.3960608094349</v>
+        <v>360.2295980564599</v>
       </c>
       <c r="V24" t="n">
-        <v>588.3960608094349</v>
+        <v>360.2295980564599</v>
       </c>
       <c r="W24" t="n">
-        <v>344.9617173750914</v>
+        <v>116.7808214123599</v>
       </c>
       <c r="X24" t="n">
-        <v>137.1102171695586</v>
+        <v>116.7808214123599</v>
       </c>
       <c r="Y24" t="n">
-        <v>137.1102171695586</v>
+        <v>116.7808214123599</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>233.6969696969697</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="C26" t="n">
-        <v>233.6969696969697</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="D26" t="n">
-        <v>233.6969696969697</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="E26" t="n">
-        <v>233.6969696969697</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="F26" t="n">
-        <v>233.6969696969697</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="G26" t="n">
-        <v>233.6969696969697</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H26" t="n">
-        <v>233.6969696969697</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I26" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U26" t="n">
-        <v>720.5656565656566</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V26" t="n">
-        <v>477.1313131313132</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W26" t="n">
-        <v>233.6969696969697</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="X26" t="n">
-        <v>233.6969696969697</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="Y26" t="n">
-        <v>233.6969696969697</v>
+        <v>710.516763498309</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20.03413265278571</v>
+        <v>76.77296163243852</v>
       </c>
       <c r="C27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>144.6375600578374</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>383.2275600578374</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N27" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O27" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P27" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>761.813405358766</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U27" t="n">
-        <v>533.5897870951551</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V27" t="n">
-        <v>298.4376788634124</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="W27" t="n">
-        <v>298.4376788634124</v>
+        <v>492.3847606029253</v>
       </c>
       <c r="X27" t="n">
-        <v>90.58617865787954</v>
+        <v>284.5332603973924</v>
       </c>
       <c r="Y27" t="n">
-        <v>20.03413265278571</v>
+        <v>76.77296163243852</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543127</v>
       </c>
       <c r="C29" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543127</v>
       </c>
       <c r="D29" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543127</v>
       </c>
       <c r="E29" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543127</v>
       </c>
       <c r="F29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.27999999994063</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935105428</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450952013</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723581055</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.1449945653449</v>
+        <v>725.2021500759371</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3399447079929</v>
+        <v>874.3971002185851</v>
       </c>
       <c r="P29" t="n">
-        <v>964.0000000000439</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q29" t="n">
-        <v>964.0000000000439</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="R29" t="n">
-        <v>964.0000000000439</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="S29" t="n">
-        <v>964.0000000000439</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="T29" t="n">
-        <v>964.0000000000439</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="U29" t="n">
-        <v>964.0000000000439</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="V29" t="n">
-        <v>749.5830303030303</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="W29" t="n">
-        <v>506.1486868686869</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="X29" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="Y29" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984127</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19.28</v>
+        <v>69.84447166430658</v>
       </c>
       <c r="C30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L30" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M30" t="n">
-        <v>613.1906659261865</v>
+        <v>304.2053859195203</v>
       </c>
       <c r="N30" t="n">
-        <v>613.1906659261865</v>
+        <v>542.8095319084027</v>
       </c>
       <c r="O30" t="n">
-        <v>851.7806659261865</v>
+        <v>781.4136778972852</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U30" t="n">
-        <v>735.7763817363891</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V30" t="n">
-        <v>500.6242735046464</v>
+        <v>728.9050472788933</v>
       </c>
       <c r="W30" t="n">
-        <v>257.1899300703029</v>
+        <v>485.4562706347933</v>
       </c>
       <c r="X30" t="n">
-        <v>49.33842986477009</v>
+        <v>277.6047704292605</v>
       </c>
       <c r="Y30" t="n">
-        <v>19.28</v>
+        <v>69.84447166430658</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="C31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="D31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="E31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="F31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280782</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203004</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757367</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="T31" t="n">
-        <v>964</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="U31" t="n">
-        <v>964</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="V31" t="n">
-        <v>964</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="W31" t="n">
-        <v>964</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="X31" t="n">
-        <v>964</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="Y31" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="C32" t="n">
-        <v>19.28</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="D32" t="n">
-        <v>19.28</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="E32" t="n">
-        <v>19.28</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="F32" t="n">
-        <v>19.28</v>
+        <v>262.7299197543127</v>
       </c>
       <c r="G32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>19.27999999994063</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>122.2389935105428</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>302.3148450952013</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>519.2904723581055</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>725.1449945653449</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>874.3399447079929</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>964.0000000000439</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>964.0000000000439</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R32" t="n">
-        <v>812.6170525847411</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S32" t="n">
-        <v>601.4856691642913</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T32" t="n">
-        <v>376.1363261702191</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U32" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V32" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W32" t="n">
-        <v>262.7143434343434</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="X32" t="n">
-        <v>262.7143434343434</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="Y32" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984127</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>69.80174936342718</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L33" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363992</v>
       </c>
       <c r="M33" t="n">
-        <v>487.8331058683492</v>
+        <v>613.2059550252816</v>
       </c>
       <c r="N33" t="n">
-        <v>542.7665223866492</v>
+        <v>656.0584510084243</v>
       </c>
       <c r="O33" t="n">
-        <v>781.3565223866492</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="P33" t="n">
-        <v>964</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q33" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R33" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S33" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T33" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U33" t="n">
-        <v>964</v>
+        <v>735.8335372470251</v>
       </c>
       <c r="V33" t="n">
-        <v>728.8478917682573</v>
+        <v>500.6814290152824</v>
       </c>
       <c r="W33" t="n">
-        <v>485.4135483339139</v>
+        <v>257.2326523711824</v>
       </c>
       <c r="X33" t="n">
-        <v>277.5620481283811</v>
+        <v>49.38115216564955</v>
       </c>
       <c r="Y33" t="n">
-        <v>69.80174936342718</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="C34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="D34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="E34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="F34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="G34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="H34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="I34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="J34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="K34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="L34" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280782</v>
       </c>
       <c r="M34" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203004</v>
       </c>
       <c r="N34" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757367</v>
       </c>
       <c r="O34" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="P34" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q34" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R34" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S34" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T34" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U34" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V34" t="n">
-        <v>964</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="W34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="X34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="Y34" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>467.0396977630861</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="C35" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984127</v>
       </c>
       <c r="D35" t="n">
-        <v>19.28</v>
+        <v>262.7299197543127</v>
       </c>
       <c r="E35" t="n">
-        <v>19.28</v>
+        <v>262.7299197543127</v>
       </c>
       <c r="F35" t="n">
-        <v>19.28</v>
+        <v>262.7299197543127</v>
       </c>
       <c r="G35" t="n">
-        <v>19.28</v>
+        <v>262.7299197543127</v>
       </c>
       <c r="H35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K35" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R35" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S35" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T35" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U35" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V35" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W35" t="n">
-        <v>953.9083846317729</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="X35" t="n">
-        <v>953.9083846317729</v>
+        <v>749.6274730425127</v>
       </c>
       <c r="Y35" t="n">
-        <v>710.4740411974295</v>
+        <v>749.6274730425127</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L36" t="n">
-        <v>249.2431058683491</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M36" t="n">
-        <v>487.8331058683492</v>
+        <v>234.8108274061909</v>
       </c>
       <c r="N36" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="O36" t="n">
-        <v>781.3565223866492</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P36" t="n">
-        <v>964</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q36" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R36" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S36" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T36" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U36" t="n">
-        <v>913.478250636573</v>
+        <v>735.8335372470251</v>
       </c>
       <c r="V36" t="n">
-        <v>678.3261424048302</v>
+        <v>500.6814290152824</v>
       </c>
       <c r="W36" t="n">
-        <v>434.8917989704868</v>
+        <v>257.2326523711824</v>
       </c>
       <c r="X36" t="n">
-        <v>227.0402987649539</v>
+        <v>49.38115216564955</v>
       </c>
       <c r="Y36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L37" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M37" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N37" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U37" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>506.1486868686869</v>
+        <v>467.0679868542089</v>
       </c>
       <c r="C38" t="n">
-        <v>506.1486868686869</v>
+        <v>467.0679868542089</v>
       </c>
       <c r="D38" t="n">
-        <v>262.7143434343434</v>
+        <v>467.0679868542089</v>
       </c>
       <c r="E38" t="n">
-        <v>19.28</v>
+        <v>467.0679868542089</v>
       </c>
       <c r="F38" t="n">
-        <v>19.28</v>
+        <v>467.0679868542089</v>
       </c>
       <c r="G38" t="n">
-        <v>19.28</v>
+        <v>223.6192102101089</v>
       </c>
       <c r="H38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>122.238993510515</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>302.3148450951736</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>519.2904723580777</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>725.1449945653171</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>874.3399447079652</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>964.0000000000161</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q38" t="n">
-        <v>964.0000000000161</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="R38" t="n">
-        <v>964.0000000000161</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="S38" t="n">
-        <v>964.0000000000161</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="T38" t="n">
-        <v>964.0000000000161</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="U38" t="n">
-        <v>964.0000000000161</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="V38" t="n">
-        <v>720.5656565656727</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="W38" t="n">
-        <v>720.5656565656727</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="X38" t="n">
-        <v>720.5656565656727</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="Y38" t="n">
-        <v>720.5656565656727</v>
+        <v>710.5167634983089</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="C39" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D39" t="n">
-        <v>19.28</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E39" t="n">
-        <v>19.28</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F39" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G39" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H39" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I39" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M39" t="n">
-        <v>473.3719638733197</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="N39" t="n">
-        <v>473.3719638733197</v>
+        <v>473.4149733950733</v>
       </c>
       <c r="O39" t="n">
-        <v>711.9619638733197</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P39" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q39" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R39" t="n">
-        <v>964</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="S39" t="n">
-        <v>964</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="T39" t="n">
-        <v>761.813405358766</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="U39" t="n">
-        <v>533.5897870951551</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="V39" t="n">
-        <v>298.4376788634124</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="W39" t="n">
-        <v>298.4376788634124</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="X39" t="n">
-        <v>90.58617865787954</v>
+        <v>862.8876260635217</v>
       </c>
       <c r="Y39" t="n">
-        <v>19.28</v>
+        <v>862.8876260635217</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C40" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D40" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E40" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F40" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T40" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U40" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V40" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W40" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X40" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y40" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>262.7143434343434</v>
+        <v>477.159602222436</v>
       </c>
       <c r="C41" t="n">
-        <v>19.28</v>
+        <v>477.159602222436</v>
       </c>
       <c r="D41" t="n">
-        <v>19.28</v>
+        <v>477.159602222436</v>
       </c>
       <c r="E41" t="n">
-        <v>19.28</v>
+        <v>477.159602222436</v>
       </c>
       <c r="F41" t="n">
-        <v>19.28</v>
+        <v>233.710825578336</v>
       </c>
       <c r="G41" t="n">
-        <v>19.28</v>
+        <v>233.710825578336</v>
       </c>
       <c r="H41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K41" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L41" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M41" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N41" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759371</v>
       </c>
       <c r="O41" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185851</v>
       </c>
       <c r="P41" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T41" t="n">
-        <v>953.9083846317729</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U41" t="n">
-        <v>749.5830303030303</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V41" t="n">
-        <v>506.1486868686869</v>
+        <v>964.057155510636</v>
       </c>
       <c r="W41" t="n">
-        <v>262.7143434343434</v>
+        <v>964.057155510636</v>
       </c>
       <c r="X41" t="n">
-        <v>262.7143434343434</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Y41" t="n">
-        <v>262.7143434343434</v>
+        <v>720.608378866536</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>428.118103226787</v>
+        <v>194.4883050441254</v>
       </c>
       <c r="C42" t="n">
-        <v>428.118103226787</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="D42" t="n">
-        <v>279.1836935655357</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="E42" t="n">
-        <v>279.1836935655357</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="F42" t="n">
-        <v>132.6491355924207</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="G42" t="n">
-        <v>132.6491355924207</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="H42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="I42" t="n">
-        <v>19.28</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K42" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L42" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M42" t="n">
-        <v>542.7665223866492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N42" t="n">
-        <v>542.7665223866492</v>
+        <v>542.8095319084027</v>
       </c>
       <c r="O42" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972852</v>
       </c>
       <c r="P42" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q42" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R42" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S42" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T42" t="n">
-        <v>906.7045548928731</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U42" t="n">
-        <v>906.7045548928731</v>
+        <v>853.5488806587122</v>
       </c>
       <c r="V42" t="n">
-        <v>671.5524466611304</v>
+        <v>853.5488806587122</v>
       </c>
       <c r="W42" t="n">
-        <v>428.118103226787</v>
+        <v>610.1001040146122</v>
       </c>
       <c r="X42" t="n">
-        <v>428.118103226787</v>
+        <v>402.2486038090793</v>
       </c>
       <c r="Y42" t="n">
-        <v>428.118103226787</v>
+        <v>194.4883050441254</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="C43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="D43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="E43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="F43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="G43" t="n">
-        <v>829.4677095097293</v>
+        <v>964.057155510636</v>
       </c>
       <c r="H43" t="n">
-        <v>829.4677095097293</v>
+        <v>964.057155510636</v>
       </c>
       <c r="I43" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="J43" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="K43" t="n">
-        <v>829.4677095097293</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="L43" t="n">
-        <v>856.7818345174422</v>
+        <v>856.8389900280782</v>
       </c>
       <c r="M43" t="n">
-        <v>895.9698727096644</v>
+        <v>896.0270282203004</v>
       </c>
       <c r="N43" t="n">
-        <v>939.6607233651007</v>
+        <v>939.7178788757367</v>
       </c>
       <c r="O43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="P43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="V43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="W43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="X43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Y43" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
     </row>
     <row r="44">
@@ -7607,76 +7607,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>90.30740735371123</v>
+        <v>728.6161971483368</v>
       </c>
       <c r="C44" t="n">
-        <v>90.30740735371123</v>
+        <v>728.6161971483368</v>
       </c>
       <c r="D44" t="n">
-        <v>90.30740735371123</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="E44" t="n">
-        <v>90.30740735371123</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="F44" t="n">
-        <v>90.30740735371123</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="G44" t="n">
-        <v>90.30740735371123</v>
+        <v>31.35113235729607</v>
       </c>
       <c r="H44" t="n">
-        <v>90.30740735371123</v>
+        <v>31.35113235729607</v>
       </c>
       <c r="I44" t="n">
-        <v>19.28</v>
+        <v>31.35113235729607</v>
       </c>
       <c r="J44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K44" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L44" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M44" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N44" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O44" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P44" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q44" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="R44" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="S44" t="n">
-        <v>802.5254372164702</v>
+        <v>953.9655401424089</v>
       </c>
       <c r="T44" t="n">
-        <v>577.1760942223981</v>
+        <v>728.6161971483368</v>
       </c>
       <c r="U44" t="n">
-        <v>333.7417507880547</v>
+        <v>728.6161971483368</v>
       </c>
       <c r="V44" t="n">
-        <v>333.7417507880547</v>
+        <v>728.6161971483368</v>
       </c>
       <c r="W44" t="n">
-        <v>90.30740735371123</v>
+        <v>728.6161971483368</v>
       </c>
       <c r="X44" t="n">
-        <v>90.30740735371123</v>
+        <v>728.6161971483368</v>
       </c>
       <c r="Y44" t="n">
-        <v>90.30740735371123</v>
+        <v>728.6161971483368</v>
       </c>
     </row>
     <row r="45">
@@ -7686,76 +7686,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>257.1899300703029</v>
+        <v>279.9389693285341</v>
       </c>
       <c r="C45" t="n">
-        <v>257.1899300703029</v>
+        <v>279.9389693285341</v>
       </c>
       <c r="D45" t="n">
-        <v>257.1899300703029</v>
+        <v>279.9389693285341</v>
       </c>
       <c r="E45" t="n">
-        <v>257.1899300703029</v>
+        <v>279.9389693285341</v>
       </c>
       <c r="F45" t="n">
-        <v>257.1899300703029</v>
+        <v>133.4044113554191</v>
       </c>
       <c r="G45" t="n">
-        <v>133.4032682452064</v>
+        <v>133.4044113554191</v>
       </c>
       <c r="H45" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="I45" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299843</v>
       </c>
       <c r="J45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K45" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L45" t="n">
-        <v>144.6375600578374</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M45" t="n">
-        <v>383.2275600578374</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N45" t="n">
-        <v>473.3719638733197</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="O45" t="n">
-        <v>711.9619638733197</v>
+        <v>712.0191193839557</v>
       </c>
       <c r="P45" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973067</v>
       </c>
       <c r="Q45" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R45" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S45" t="n">
-        <v>964</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T45" t="n">
-        <v>964</v>
+        <v>761.870560869402</v>
       </c>
       <c r="U45" t="n">
-        <v>735.7763817363891</v>
+        <v>758.5398542043768</v>
       </c>
       <c r="V45" t="n">
-        <v>500.6242735046464</v>
+        <v>523.3877459726341</v>
       </c>
       <c r="W45" t="n">
-        <v>257.1899300703029</v>
+        <v>279.9389693285341</v>
       </c>
       <c r="X45" t="n">
-        <v>257.1899300703029</v>
+        <v>279.9389693285341</v>
       </c>
       <c r="Y45" t="n">
-        <v>257.1899300703029</v>
+        <v>279.9389693285341</v>
       </c>
     </row>
     <row r="46">
@@ -7765,76 +7765,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="C46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="D46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="E46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="F46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="G46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="H46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="I46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="J46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="K46" t="n">
-        <v>19.28</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="L46" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280782</v>
       </c>
       <c r="M46" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203004</v>
       </c>
       <c r="N46" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757367</v>
       </c>
       <c r="O46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="P46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="Q46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="R46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="S46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="T46" t="n">
-        <v>153.8122904902707</v>
+        <v>964.057155510636</v>
       </c>
       <c r="U46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="V46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="W46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="X46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
       <c r="Y46" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203653</v>
       </c>
     </row>
   </sheetData>
@@ -7974,7 +7974,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P2" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q2" t="n">
         <v>212.3149906599047</v>
@@ -8044,19 +8044,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M3" t="n">
-        <v>383.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N3" t="n">
-        <v>174.5990611343274</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O3" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P3" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q3" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R3" t="n">
         <v>45.52166981132082</v>
@@ -8202,7 +8202,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M5" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N5" t="n">
         <v>437.3469244119842</v>
@@ -8275,19 +8275,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K6" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L6" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M6" t="n">
-        <v>311.9985353972331</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N6" t="n">
-        <v>131.3417120833333</v>
+        <v>186.8580120236956</v>
       </c>
       <c r="O6" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P6" t="n">
         <v>318.4627686399372</v>
@@ -8433,7 +8433,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L8" t="n">
         <v>417.6612145504504</v>
@@ -8518,19 +8518,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M9" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N9" t="n">
-        <v>301.2062135585481</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>142.5962444444444</v>
+        <v>242.4075215744184</v>
       </c>
       <c r="P9" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q9" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8670,7 +8670,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L11" t="n">
         <v>417.6612145504504</v>
@@ -8758,10 +8758,10 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>357.73449794694</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O12" t="n">
-        <v>383.5962444444444</v>
+        <v>369.031319612638</v>
       </c>
       <c r="P12" t="n">
         <v>318.4627686399372</v>
@@ -8907,7 +8907,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L14" t="n">
         <v>417.6612145504504</v>
@@ -8986,19 +8986,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M15" t="n">
-        <v>311.9985353972331</v>
+        <v>197.6503338623804</v>
       </c>
       <c r="N15" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O15" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P15" t="n">
         <v>318.4627686399372</v>
@@ -9144,7 +9144,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L17" t="n">
         <v>417.6612145504504</v>
@@ -9223,22 +9223,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M18" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>372.3417120833333</v>
+        <v>231.1529892133071</v>
       </c>
       <c r="O18" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P18" t="n">
-        <v>295.1415200271288</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q18" t="n">
         <v>210.0772877358491</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L21" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>197.6223334354527</v>
+        <v>241.9453110519922</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889305</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>241.9453110519922</v>
       </c>
       <c r="N24" t="n">
-        <v>186.8300115967677</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9937,22 +9937,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N27" t="n">
-        <v>222.3966654323053</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343890231</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10171,22 +10171,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K30" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>197.6503338623804</v>
       </c>
       <c r="N30" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P30" t="n">
-        <v>247.3272701151519</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
         <v>139.9817740860215</v>
@@ -10329,7 +10329,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>324.0888343890231</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
@@ -10408,25 +10408,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996773</v>
       </c>
       <c r="N33" t="n">
-        <v>186.8300115967677</v>
+        <v>174.6270615612552</v>
       </c>
       <c r="O33" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P33" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10566,7 +10566,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
@@ -10648,22 +10648,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>383.1340339220183</v>
+        <v>359.8407857361377</v>
       </c>
       <c r="N36" t="n">
-        <v>186.8300115967677</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O36" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P36" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q36" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10803,7 +10803,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.0888343889351</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
@@ -10882,19 +10882,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>241.9030217474054</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>357.7767872515267</v>
       </c>
       <c r="O39" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
@@ -11040,7 +11040,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
@@ -11119,19 +11119,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M42" t="n">
-        <v>311.9985353972331</v>
+        <v>383.1483227996773</v>
       </c>
       <c r="N42" t="n">
-        <v>131.3417120833333</v>
+        <v>186.8580120236954</v>
       </c>
       <c r="O42" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221034</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
@@ -11286,7 +11286,7 @@
         <v>449.5135334928325</v>
       </c>
       <c r="N44" t="n">
-        <v>437.2903462297383</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O44" t="n">
         <v>380.8001812627454</v>
@@ -11356,19 +11356,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K45" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L45" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M45" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996773</v>
       </c>
       <c r="N45" t="n">
-        <v>222.3966654323053</v>
+        <v>357.7767872515267</v>
       </c>
       <c r="O45" t="n">
-        <v>383.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
         <v>318.4627686399372</v>
@@ -22552,28 +22552,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R2" t="n">
-        <v>128.7122370915265</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U2" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V2" t="n">
-        <v>86.7522584701349</v>
+        <v>115.4668728266929</v>
       </c>
       <c r="W2" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X2" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y2" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="3">
@@ -22583,31 +22583,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>116.5166517800744</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>172.7084989883157</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D3" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -22643,16 +22643,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W3" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="4">
@@ -22683,10 +22683,10 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I4" t="n">
-        <v>155.4504749272583</v>
+        <v>115.622687458563</v>
       </c>
       <c r="J4" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>22.26949182588285</v>
@@ -22707,10 +22707,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R4" t="n">
-        <v>130.2684670434959</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S4" t="n">
         <v>224.0165980369723</v>
@@ -22741,13 +22741,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C5" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D5" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E5" t="n">
         <v>381.9303700722618</v>
@@ -22762,10 +22762,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R5" t="n">
         <v>149.8691179411497</v>
@@ -22804,13 +22804,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W5" t="n">
-        <v>128.3840468569763</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X5" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y5" t="n">
-        <v>145.2379386560536</v>
+        <v>173.9525530126116</v>
       </c>
     </row>
     <row r="6">
@@ -22820,16 +22820,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>145.0692123933839</v>
@@ -22838,13 +22838,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2354442364965</v>
+        <v>26.92171639560435</v>
       </c>
       <c r="I6" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -22868,28 +22868,28 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W6" t="n">
-        <v>247.9164776688802</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X6" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y6" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22944,10 +22944,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>177.2933913771695</v>
+        <v>130.2684670434958</v>
       </c>
       <c r="S7" t="n">
         <v>224.0165980369723</v>
@@ -22962,7 +22962,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W7" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X7" t="n">
         <v>225.7096553890372</v>
@@ -22978,10 +22978,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>141.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C8" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D8" t="n">
         <v>354.683041620683</v>
@@ -22993,16 +22993,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H8" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I8" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>10.13979328157633</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,7 +23023,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
         <v>149.8691179411497</v>
@@ -23047,7 +23047,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>183.9558378705984</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="9">
@@ -23057,7 +23057,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
         <v>172.7084989883157</v>
@@ -23108,25 +23108,25 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>217.4210772589755</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>10.69498316091961</v>
+        <v>247.8610253924609</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="10">
@@ -23151,7 +23151,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>34.80401177309074</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H10" t="n">
         <v>162.2271725074396</v>
@@ -23181,10 +23181,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>177.2933913771695</v>
+        <v>130.2684670434958</v>
       </c>
       <c r="S10" t="n">
         <v>224.0165980369723</v>
@@ -23224,19 +23224,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E11" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G11" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H11" t="n">
-        <v>137.1927013303119</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I11" t="n">
-        <v>210.4758895704059</v>
+        <v>158.0503210826583</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -23263,7 +23263,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>209.0200695862453</v>
@@ -23294,25 +23294,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>103.7072024513138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
         <v>89.39663285141508</v>
@@ -23342,22 +23342,22 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>251.6949831609196</v>
+        <v>247.1144340662031</v>
       </c>
       <c r="X12" t="n">
         <v>205.7729852034775</v>
@@ -23394,10 +23394,10 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>155.4504749272583</v>
+        <v>140.6136200195524</v>
       </c>
       <c r="J13" t="n">
-        <v>68.603747608882</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23415,10 +23415,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R13" t="n">
         <v>177.2933913771695</v>
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C14" t="n">
         <v>365.2728917710076</v>
@@ -23464,19 +23464,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G14" t="n">
-        <v>415.302737515135</v>
+        <v>174.2884486374761</v>
       </c>
       <c r="H14" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810815</v>
       </c>
       <c r="I14" t="n">
-        <v>210.4758895704059</v>
+        <v>169.9996104372709</v>
       </c>
       <c r="J14" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -23497,10 +23497,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>209.0200695862453</v>
@@ -23515,13 +23515,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W14" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X14" t="n">
-        <v>157.4583006784691</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y14" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="15">
@@ -23534,7 +23534,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
-        <v>26.57065165286144</v>
+        <v>27.26179070270035</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -23555,7 +23555,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23631,7 +23631,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>137.8921792844459</v>
+        <v>140.6136200195524</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -23652,7 +23652,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>86.16204325169439</v>
@@ -23695,10 +23695,10 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D17" t="n">
-        <v>354.683041620683</v>
+        <v>113.668752743024</v>
       </c>
       <c r="E17" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946028</v>
       </c>
       <c r="F17" t="n">
         <v>406.8760457417114</v>
@@ -23707,13 +23707,13 @@
         <v>415.302737515135</v>
       </c>
       <c r="H17" t="n">
-        <v>337.677891686173</v>
+        <v>98.46051323810815</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>20.13049249612121</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23734,7 +23734,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>149.8691179411497</v>
@@ -23749,13 +23749,13 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V17" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W17" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X17" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y17" t="n">
         <v>386.2379386560536</v>
@@ -23831,7 +23831,7 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>247.1698863426223</v>
+        <v>247.1144340662033</v>
       </c>
       <c r="X18" t="n">
         <v>205.7729852034775</v>
@@ -23901,7 +23901,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T19" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
         <v>286.3190293564909</v>
@@ -23916,7 +23916,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y19" t="n">
-        <v>218.5846533520948</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
     <row r="20">
@@ -23935,19 +23935,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946028</v>
       </c>
       <c r="F20" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>415.302737515135</v>
+        <v>174.2884486374761</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I20" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -23977,25 +23977,25 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>221.286353491095</v>
       </c>
       <c r="U20" t="n">
-        <v>230.1887720582133</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783946</v>
       </c>
     </row>
     <row r="21">
@@ -24005,28 +24005,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>22.33474951932527</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>41.02385161157994</v>
       </c>
       <c r="I21" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0.7465913262578567</v>
@@ -24053,13 +24053,13 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>225.9413820809748</v>
@@ -24068,13 +24068,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24084,10 +24084,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>179.8319801819373</v>
+        <v>46.64501259656927</v>
       </c>
       <c r="C22" t="n">
-        <v>34.05985351325981</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D22" t="n">
         <v>148.6154730182124</v>
@@ -24163,10 +24163,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858216</v>
       </c>
       <c r="C23" t="n">
-        <v>153.0000917709961</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
         <v>354.683041620683</v>
@@ -24217,22 +24217,22 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>223.0958495641314</v>
+        <v>10.81046392068936</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3456529078365</v>
+        <v>10.3313640301775</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783946</v>
       </c>
     </row>
     <row r="24">
@@ -24242,10 +24242,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>70.7550934569995</v>
       </c>
       <c r="C24" t="n">
-        <v>56.05658399045272</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
         <v>147.4450655646388</v>
@@ -24266,7 +24266,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24299,16 +24299,16 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
         <v>205.6826957773044</v>
@@ -24342,7 +24342,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I25" t="n">
-        <v>155.4504749272583</v>
+        <v>22.26350734189026</v>
       </c>
       <c r="J25" t="n">
         <v>93.35918011667277</v>
@@ -24372,7 +24372,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S25" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T25" t="n">
         <v>227.9455894282815</v>
@@ -24400,7 +24400,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>382.7338416634806</v>
+        <v>192.3884445891958</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
@@ -24412,16 +24412,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G26" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H26" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I26" t="n">
-        <v>10.15237892501841</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24445,7 +24445,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>149.8691179411497</v>
@@ -24457,19 +24457,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="27">
@@ -24482,7 +24482,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>116.5381899775701</v>
       </c>
       <c r="D27" t="n">
         <v>147.4450655646388</v>
@@ -24533,22 +24533,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>135.8361702322615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -24637,31 +24637,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858216</v>
       </c>
       <c r="C29" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D29" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F29" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G29" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I29" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
-        <v>11.94928935455374</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -24682,7 +24682,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>149.8691179411497</v>
@@ -24697,13 +24697,13 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>115.4794584700915</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>108.240968717413</v>
+        <v>146.9462822885158</v>
       </c>
       <c r="X29" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y29" t="n">
         <v>386.2379386560536</v>
@@ -24719,7 +24719,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>122.6508037197628</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
@@ -24773,19 +24773,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>175.924850211182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -24843,7 +24843,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180149</v>
       </c>
       <c r="S31" t="n">
         <v>224.0165980369723</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>85.39768576672677</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="32">
@@ -24877,7 +24877,7 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
         <v>354.683041620683</v>
@@ -24886,10 +24886,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>174.2884486374761</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24898,7 +24898,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
-        <v>11.94928935455374</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>139.0578899993196</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>349.240968717413</v>
+        <v>136.9555830739708</v>
       </c>
       <c r="X32" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783946</v>
       </c>
     </row>
     <row r="33">
@@ -24956,7 +24956,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>122.6919671185228</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
@@ -25010,19 +25010,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>175.8836868124219</v>
       </c>
     </row>
     <row r="34">
@@ -25092,10 +25092,10 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V34" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W34" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
         <v>225.7096553890372</v>
@@ -25111,13 +25111,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>162.9907909855523</v>
+        <v>124.2586028933486</v>
       </c>
       <c r="D35" t="n">
-        <v>113.683041620683</v>
+        <v>113.668752743024</v>
       </c>
       <c r="E35" t="n">
         <v>381.9303700722618</v>
@@ -25129,7 +25129,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810815</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25156,7 +25156,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
         <v>149.8691179411497</v>
@@ -25174,13 +25174,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>349.240968717413</v>
+        <v>136.9555830739708</v>
       </c>
       <c r="X35" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y35" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="36">
@@ -25247,19 +25247,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>175.924850211182</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>175.8836868124219</v>
       </c>
     </row>
     <row r="37">
@@ -25323,13 +25323,13 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T37" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U37" t="n">
         <v>286.3190293564909</v>
       </c>
       <c r="V37" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W37" t="n">
         <v>286.522998336591</v>
@@ -25348,25 +25348,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>170.4610416634646</v>
+        <v>141.7195527858216</v>
       </c>
       <c r="C38" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>415.302737515135</v>
+        <v>174.2884486374761</v>
       </c>
       <c r="H38" t="n">
-        <v>339.4748021157671</v>
+        <v>137.1801156868699</v>
       </c>
       <c r="I38" t="n">
         <v>210.4758895704059</v>
@@ -25393,7 +25393,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>149.8691179411497</v>
@@ -25408,7 +25408,7 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V38" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
         <v>349.240968717413</v>
@@ -25417,7 +25417,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y38" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783946</v>
       </c>
     </row>
     <row r="39">
@@ -25427,31 +25427,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>166.5331836498673</v>
+        <v>121.2443095168951</v>
       </c>
       <c r="C39" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -25475,28 +25475,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>135.0895789060036</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -25521,7 +25521,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309074</v>
       </c>
       <c r="H40" t="n">
         <v>162.2271725074396</v>
@@ -25560,7 +25560,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T40" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
         <v>286.3190293564909</v>
@@ -25585,10 +25585,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858216</v>
       </c>
       <c r="C41" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
@@ -25597,13 +25597,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G41" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
-        <v>339.4748021157671</v>
+        <v>127.1894164723251</v>
       </c>
       <c r="I41" t="n">
         <v>210.4758895704059</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25642,19 +25642,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>49.06355212238131</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783946</v>
       </c>
     </row>
     <row r="42">
@@ -25667,28 +25667,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25718,22 +25718,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T42" t="n">
-        <v>143.442238038766</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>116.5381899775702</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -25758,13 +25758,13 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>34.80401177309074</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H43" t="n">
         <v>162.2271725074396</v>
       </c>
       <c r="I43" t="n">
-        <v>155.4504749272583</v>
+        <v>22.26350734189029</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -25828,25 +25828,25 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D44" t="n">
-        <v>354.683041620683</v>
+        <v>146.4192052328707</v>
       </c>
       <c r="E44" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F44" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G44" t="n">
-        <v>415.302737515135</v>
+        <v>174.2884486374761</v>
       </c>
       <c r="H44" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I44" t="n">
-        <v>140.1587562902318</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J44" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -25870,7 +25870,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S44" t="n">
         <v>209.0200695862453</v>
@@ -25879,13 +25879,13 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
       </c>
       <c r="W44" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X44" t="n">
         <v>369.731100678469</v>
@@ -25913,10 +25913,10 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F45" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>14.79472195636507</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -25955,16 +25955,16 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T45" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>222.6439824825999</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326061</v>
       </c>
       <c r="X45" t="n">
         <v>205.7729852034775</v>
@@ -26001,7 +26001,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I46" t="n">
-        <v>22.26350734189026</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J46" t="n">
         <v>93.35918011667277</v>
@@ -26037,7 +26037,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U46" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611644</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611644</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611642</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>456932.5473417963</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611644</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>456932.5473418062</v>
+        <v>456941.8494611644</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>456932.5473418062</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>456932.5473417967</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="C2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="D2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="E2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="F2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="G2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="H2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="I2" t="n">
-        <v>124617.9674568535</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="J2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="K2" t="n">
-        <v>124617.9674568562</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="L2" t="n">
-        <v>124617.9674568562</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="M2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="N2" t="n">
-        <v>124617.9674568536</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="O2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="P2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
     </row>
     <row r="3">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80764.643</v>
+        <v>80769.43153154773</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26337,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>63056.204</v>
+        <v>63059.94259910625</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="C4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="D4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="E4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="F4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039668</v>
       </c>
       <c r="G4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966173</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966283</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="L4" t="n">
-        <v>179.5221438966283</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="M4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="N4" t="n">
-        <v>179.5221438966178</v>
+        <v>179.5324977039668</v>
       </c>
       <c r="O4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="P4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039668</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="C5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="D5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="E5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="F5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="G5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="P5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-4606.597687043475</v>
+        <v>-4609.728394514081</v>
       </c>
       <c r="C6" t="n">
-        <v>76158.04531295656</v>
+        <v>76159.70313703362</v>
       </c>
       <c r="D6" t="n">
-        <v>76158.04531295659</v>
+        <v>76159.70313703365</v>
       </c>
       <c r="E6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="F6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="G6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="H6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="I6" t="n">
-        <v>109785.6453129569</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="J6" t="n">
-        <v>46729.44131295655</v>
+        <v>46727.36053792742</v>
       </c>
       <c r="K6" t="n">
-        <v>109785.6453129595</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="L6" t="n">
-        <v>109785.6453129596</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="M6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="N6" t="n">
-        <v>109785.645312957</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="O6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="P6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370337</v>
       </c>
     </row>
   </sheetData>
@@ -26727,49 +26727,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="L4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27185,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34629,7 +34629,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P2" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -34699,19 +34699,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M3" t="n">
-        <v>241</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N3" t="n">
-        <v>43.25734905099405</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O3" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q3" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -34857,7 +34857,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M5" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N5" t="n">
         <v>207.9338608153932</v>
@@ -34930,19 +34930,19 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M6" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="O6" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P6" t="n">
         <v>184.4883612256069</v>
@@ -35088,7 +35088,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L8" t="n">
         <v>181.8947995804632</v>
@@ -35173,19 +35173,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M9" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N9" t="n">
-        <v>169.8645014752148</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>99.8112771299739</v>
       </c>
       <c r="P9" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35325,7 +35325,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L11" t="n">
         <v>181.8947995804632</v>
@@ -35413,10 +35413,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>226.3927858636066</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O12" t="n">
-        <v>241</v>
+        <v>226.4350751681936</v>
       </c>
       <c r="P12" t="n">
         <v>184.4883612256069</v>
@@ -35562,7 +35562,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L14" t="n">
         <v>181.8947995804632</v>
@@ -35571,7 +35571,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N14" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153931</v>
       </c>
       <c r="O14" t="n">
         <v>150.7019698410586</v>
@@ -35641,19 +35641,19 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M15" t="n">
-        <v>169.8645014752148</v>
+        <v>55.51629994036207</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="O15" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P15" t="n">
         <v>184.4883612256069</v>
@@ -35799,7 +35799,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L17" t="n">
         <v>181.8947995804632</v>
@@ -35878,22 +35878,22 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M18" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>241</v>
+        <v>99.81127712997385</v>
       </c>
       <c r="O18" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P18" t="n">
-        <v>161.1671126127986</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q18" t="n">
         <v>70.09551364982758</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L21" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>55.48829951343433</v>
+        <v>99.81127712997385</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.99898334395</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>99.81127712997385</v>
       </c>
       <c r="N24" t="n">
-        <v>55.48829951343436</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36592,22 +36592,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N27" t="n">
-        <v>91.05495334897201</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833440426</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36826,22 +36826,22 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>55.51629994036207</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>241.014288877659</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P30" t="n">
-        <v>113.3528627008217</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -36984,7 +36984,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>103.9989833440426</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
@@ -37063,25 +37063,25 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="N33" t="n">
-        <v>55.48829951343436</v>
+        <v>43.28534947792193</v>
       </c>
       <c r="O33" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P33" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37221,7 +37221,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
@@ -37303,22 +37303,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>241</v>
+        <v>217.7067518141194</v>
       </c>
       <c r="N36" t="n">
-        <v>55.48829951343436</v>
+        <v>241.014288877659</v>
       </c>
       <c r="O36" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P36" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37458,7 +37458,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>103.9989833439546</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
@@ -37473,7 +37473,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P38" t="n">
-        <v>90.5657124162131</v>
+        <v>90.56571241621288</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37537,19 +37537,19 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>99.76898782538704</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>226.4350751681934</v>
       </c>
       <c r="O39" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
@@ -37695,7 +37695,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
@@ -37774,19 +37774,19 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M42" t="n">
-        <v>169.8645014752148</v>
+        <v>241.014288877659</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>55.51629994036207</v>
       </c>
       <c r="O42" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
@@ -37941,13 +37941,13 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N44" t="n">
-        <v>207.8772826331474</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O44" t="n">
         <v>150.7019698410586</v>
       </c>
       <c r="P44" t="n">
-        <v>90.5657124162131</v>
+        <v>90.56571241621288</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38011,19 +38011,19 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M45" t="n">
-        <v>241</v>
+        <v>241.014288877659</v>
       </c>
       <c r="N45" t="n">
-        <v>91.05495334897201</v>
+        <v>226.4350751681934</v>
       </c>
       <c r="O45" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>184.4883612256069</v>
